--- a/artfynd/A 15865-2024 artfynd.xlsx
+++ b/artfynd/A 15865-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125478218</v>
+        <v>125478219</v>
       </c>
       <c r="B2" t="n">
-        <v>96982</v>
+        <v>98923</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>222309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549909</v>
+        <v>549956</v>
       </c>
       <c r="R2" t="n">
-        <v>6374714</v>
+        <v>6374686</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125478219</v>
+        <v>125478218</v>
       </c>
       <c r="B3" t="n">
-        <v>98753</v>
+        <v>97150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222309</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549956</v>
+        <v>549909</v>
       </c>
       <c r="R3" t="n">
-        <v>6374686</v>
+        <v>6374714</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,7 +892,7 @@
         <v>125478220</v>
       </c>
       <c r="B4" t="n">
-        <v>98726</v>
+        <v>98896</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 15865-2024 artfynd.xlsx
+++ b/artfynd/A 15865-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125478219</v>
+        <v>125478218</v>
       </c>
       <c r="B2" t="n">
-        <v>98923</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222309</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backstarr</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex ericetorum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549956</v>
+        <v>549909</v>
       </c>
       <c r="R2" t="n">
-        <v>6374686</v>
+        <v>6374714</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -782,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125478218</v>
+        <v>125478219</v>
       </c>
       <c r="B3" t="n">
-        <v>97150</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98978</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>222309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Backstarr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Carex ericetorum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549909</v>
+        <v>549956</v>
       </c>
       <c r="R3" t="n">
-        <v>6374714</v>
+        <v>6374686</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,12 +882,7 @@
         <v>125478220</v>
       </c>
       <c r="B4" t="n">
-        <v>98896</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15865-2024 artfynd.xlsx
+++ b/artfynd/A 15865-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125478218</v>
       </c>
       <c r="B2" t="n">
-        <v>97205</v>
+        <v>97212</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125478219</v>
       </c>
       <c r="B3" t="n">
-        <v>98978</v>
+        <v>98985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125478220</v>
       </c>
       <c r="B4" t="n">
-        <v>98951</v>
+        <v>98958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15865-2024 artfynd.xlsx
+++ b/artfynd/A 15865-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125478218</v>
       </c>
       <c r="B2" t="n">
-        <v>97212</v>
+        <v>97215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125478219</v>
       </c>
       <c r="B3" t="n">
-        <v>98985</v>
+        <v>98988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125478220</v>
       </c>
       <c r="B4" t="n">
-        <v>98958</v>
+        <v>98961</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15865-2024 artfynd.xlsx
+++ b/artfynd/A 15865-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125478218</v>
       </c>
       <c r="B2" t="n">
-        <v>97215</v>
+        <v>97219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125478219</v>
       </c>
       <c r="B3" t="n">
-        <v>98988</v>
+        <v>98992</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125478220</v>
       </c>
       <c r="B4" t="n">
-        <v>98961</v>
+        <v>98965</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15865-2024 artfynd.xlsx
+++ b/artfynd/A 15865-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125478218</v>
       </c>
       <c r="B2" t="n">
-        <v>97219</v>
+        <v>97220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125478219</v>
       </c>
       <c r="B3" t="n">
-        <v>98992</v>
+        <v>98993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125478220</v>
       </c>
       <c r="B4" t="n">
-        <v>98965</v>
+        <v>98966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15865-2024 artfynd.xlsx
+++ b/artfynd/A 15865-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125478218</v>
       </c>
       <c r="B2" t="n">
-        <v>97220</v>
+        <v>97222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125478219</v>
       </c>
       <c r="B3" t="n">
-        <v>98993</v>
+        <v>98995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125478220</v>
       </c>
       <c r="B4" t="n">
-        <v>98966</v>
+        <v>98968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
